--- a/data/trans_orig/Q5402-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2007</t>
+          <t>Población según si son capaces de prepararse la comida en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85425</t>
+          <t>85987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101960</t>
+          <t>101127</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>121581</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137725</t>
+          <t>137966</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>213854</t>
+          <t>212515</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236127</t>
+          <t>236233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29360</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113125</t>
+          <t>114059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131015</t>
+          <t>130584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151884</t>
+          <t>151697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170644</t>
+          <t>169878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271913</t>
+          <t>272195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296284</t>
+          <t>297295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80910</t>
+          <t>81607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95796</t>
+          <t>96313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111088</t>
+          <t>111656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126547</t>
+          <t>126095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197156</t>
+          <t>196978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219135</t>
+          <t>219243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40553</t>
+          <t>40380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114507</t>
+          <t>114311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127283</t>
+          <t>127760</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>167456</t>
+          <t>166605</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>187925</t>
+          <t>186491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,47 +2377,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>300234</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>286262</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>311426</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>86,77%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>82,74%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>90,01%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>300234</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>285205</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>311735</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>82,43%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>36846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51806</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80333</t>
+          <t>79749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>62253</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62298</t>
+          <t>63520</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>78899</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>117050</t>
+          <t>115365</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>412889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>443373</t>
+          <t>443230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>572581</t>
+          <t>571453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>608600</t>
+          <t>607620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>998075</t>
+          <t>994367</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1043331</t>
+          <t>1041130</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2012</t>
+          <t>Población según si son capaces de prepararse la comida en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30146</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100957</t>
+          <t>101941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120861</t>
+          <t>121378</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126882</t>
+          <t>127815</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147456</t>
+          <t>147670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236141</t>
+          <t>237790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>265218</t>
+          <t>263857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>27348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35920</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>32832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57903</t>
+          <t>57367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>36440</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>32045</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60028</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103938</t>
+          <t>104091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127576</t>
+          <t>126918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130021</t>
+          <t>128681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153489</t>
+          <t>154556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>240698</t>
+          <t>241001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275265</t>
+          <t>275572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23447</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24892</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>42839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>29909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>41205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>71287</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89366</t>
+          <t>89990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93404</t>
+          <t>94641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115228</t>
+          <t>116067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171229</t>
+          <t>171194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>199697</t>
+          <t>200462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>22622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>40690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34667</t>
+          <t>33881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58121</t>
+          <t>56364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>116644</t>
+          <t>116587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138576</t>
+          <t>139213</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192902</t>
+          <t>192213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216075</t>
+          <t>215073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>315322</t>
+          <t>316195</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>347728</t>
+          <t>346649</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>41497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>70429</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>60344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94950</t>
+          <t>95538</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>109837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156254</t>
+          <t>156214</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49285</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83806</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60221</t>
+          <t>60809</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94618</t>
+          <t>94463</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117651</t>
+          <t>120702</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>168529</t>
+          <t>167168</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>416624</t>
+          <t>417477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>458060</t>
+          <t>459168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>567038</t>
+          <t>564794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>613058</t>
+          <t>612081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>998509</t>
+          <t>998660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1061398</t>
+          <t>1062279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2016</t>
+          <t>Población según si son capaces de prepararse la comida en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>21839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41323</t>
+          <t>40189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104807</t>
+          <t>105525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121436</t>
+          <t>121447</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130450</t>
+          <t>129205</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>151668</t>
+          <t>152045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241485</t>
+          <t>241645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>269235</t>
+          <t>269294</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>22223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>24445</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>46864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129253</t>
+          <t>129812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146745</t>
+          <t>146934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174232</t>
+          <t>176183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198201</t>
+          <t>199133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>311392</t>
+          <t>310098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>341643</t>
+          <t>340624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>18964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23799</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14212</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33105</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92025</t>
+          <t>91151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105878</t>
+          <t>105769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110074</t>
+          <t>109587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129727</t>
+          <t>129716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207761</t>
+          <t>207987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231103</t>
+          <t>231378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24054</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36174</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52858</t>
+          <t>49962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147358</t>
+          <t>146799</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162336</t>
+          <t>162482</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191011</t>
+          <t>190638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>218212</t>
+          <t>217431</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>345493</t>
+          <t>345759</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>375313</t>
+          <t>375442</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>47274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>68412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>68221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106000</t>
+          <t>106613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61979</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54947</t>
+          <t>55035</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90475</t>
+          <t>93122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,47 +7744,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>118919</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>96723</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>141925</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>118919</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>99039</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>142262</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>491258</t>
+          <t>491916</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>522793</t>
+          <t>522488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>633936</t>
+          <t>631389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>679766</t>
+          <t>678434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1135936</t>
+          <t>1134626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1192566</t>
+          <t>1193388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de prepararse la comida en 2023</t>
+          <t>Población según si son capaces de prepararse la comida en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>24201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>15877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46171</t>
+          <t>46961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,49 +8397,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>19,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>28249</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22556</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34323</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>19,16%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28249</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22687</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34684</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>110</t>
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>40584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101211</t>
+          <t>101453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118048</t>
+          <t>118458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>121946</t>
+          <t>122113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136799</t>
+          <t>137166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>228488</t>
+          <t>226588</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251058</t>
+          <t>249924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>27700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43415</t>
+          <t>41470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>23069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>37949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124449</t>
+          <t>123435</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138994</t>
+          <t>138336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157104</t>
+          <t>157147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174683</t>
+          <t>173942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285476</t>
+          <t>287103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309121</t>
+          <t>309721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39066</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114196</t>
+          <t>114360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127202</t>
+          <t>126815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298245</t>
+          <t>299903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354768</t>
+          <t>354324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424938</t>
+          <t>425224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>483916</t>
+          <t>485241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28367</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43153</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40720</t>
+          <t>40487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41629</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63164</t>
+          <t>60415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163950</t>
+          <t>163624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180344</t>
+          <t>179300</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212457</t>
+          <t>212619</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231842</t>
+          <t>232139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>380798</t>
+          <t>381488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>407824</t>
+          <t>406801</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59154</t>
+          <t>59650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>39638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98487</t>
+          <t>99158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>80152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149074</t>
+          <t>147471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52112</t>
+          <t>52417</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74898</t>
+          <t>76764</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58735</t>
+          <t>57215</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135842</t>
+          <t>135659</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110155</t>
+          <t>108064</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196453</t>
+          <t>198804</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522579</t>
+          <t>519871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>550950</t>
+          <t>549743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>803025</t>
+          <t>801896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>935986</t>
+          <t>934419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1341421</t>
+          <t>1342454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1487986</t>
+          <t>1498299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5402-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5402-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25965</t>
+          <t>25915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85987</t>
+          <t>85059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101127</t>
+          <t>101162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>120626</t>
+          <t>120968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137966</t>
+          <t>138687</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>212515</t>
+          <t>212773</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236233</t>
+          <t>235558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35440</t>
+          <t>35578</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114059</t>
+          <t>113632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130584</t>
+          <t>130746</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151697</t>
+          <t>152709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169878</t>
+          <t>170476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272195</t>
+          <t>271972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297295</t>
+          <t>296267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81607</t>
+          <t>81759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96313</t>
+          <t>96078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111656</t>
+          <t>111405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>126489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196978</t>
+          <t>197727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219243</t>
+          <t>218814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40380</t>
+          <t>40876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114311</t>
+          <t>114651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127760</t>
+          <t>128003</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166605</t>
+          <t>166072</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>186491</t>
+          <t>188386</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>286262</t>
+          <t>287132</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>311426</t>
+          <t>312383</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>48456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79749</t>
+          <t>77673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36290</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62253</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>35756</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>115365</t>
+          <t>114224</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>412889</t>
+          <t>413377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>443230</t>
+          <t>443809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>571453</t>
+          <t>572975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>607620</t>
+          <t>608287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>994367</t>
+          <t>994755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1041130</t>
+          <t>1043104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39237</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101941</t>
+          <t>101919</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121378</t>
+          <t>121757</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127815</t>
+          <t>129270</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147670</t>
+          <t>147999</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237790</t>
+          <t>236871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>263857</t>
+          <t>265085</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>32285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57367</t>
+          <t>58179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31314</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36440</t>
+          <t>34824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>58313</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104091</t>
+          <t>104021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126918</t>
+          <t>127429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128681</t>
+          <t>128635</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154556</t>
+          <t>153253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241001</t>
+          <t>241721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275572</t>
+          <t>274853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>24122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24646</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12737</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41205</t>
+          <t>41300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71287</t>
+          <t>71631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89990</t>
+          <t>89542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94641</t>
+          <t>94408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116067</t>
+          <t>116729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171194</t>
+          <t>172715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200462</t>
+          <t>199763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>40881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56364</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>116587</t>
+          <t>114839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139213</t>
+          <t>138047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192213</t>
+          <t>191007</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>215073</t>
+          <t>214555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>316195</t>
+          <t>317287</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>346649</t>
+          <t>349226</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41497</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70429</t>
+          <t>71179</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60344</t>
+          <t>58476</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95538</t>
+          <t>92905</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109837</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156214</t>
+          <t>153213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>49865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82120</t>
+          <t>84086</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60809</t>
+          <t>59792</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94463</t>
+          <t>92944</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120702</t>
+          <t>119357</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167168</t>
+          <t>164694</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>417477</t>
+          <t>417026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>459168</t>
+          <t>459388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>564794</t>
+          <t>568970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>612081</t>
+          <t>614563</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>998660</t>
+          <t>997398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1062279</t>
+          <t>1057164</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21839</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>41769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26567</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105525</t>
+          <t>104939</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121447</t>
+          <t>122269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129205</t>
+          <t>130556</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>152045</t>
+          <t>152013</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241645</t>
+          <t>241470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>269294</t>
+          <t>268281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>20704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>30413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24445</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46864</t>
+          <t>47133</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129812</t>
+          <t>128159</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146934</t>
+          <t>146326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176183</t>
+          <t>175674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199133</t>
+          <t>198692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>310098</t>
+          <t>311812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340624</t>
+          <t>340152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91151</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105769</t>
+          <t>105426</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109587</t>
+          <t>110659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129716</t>
+          <t>129856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207987</t>
+          <t>206918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231378</t>
+          <t>231550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>25199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36692</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49962</t>
+          <t>53716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146799</t>
+          <t>147127</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162482</t>
+          <t>162848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190638</t>
+          <t>191427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>217431</t>
+          <t>217293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>345759</t>
+          <t>343894</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>375442</t>
+          <t>376591</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>25834</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47274</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68412</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68221</t>
+          <t>67230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106613</t>
+          <t>104438</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36332</t>
+          <t>37206</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61517</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55035</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93122</t>
+          <t>90620</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96723</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>141925</t>
+          <t>141303</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>491916</t>
+          <t>491892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>522488</t>
+          <t>523857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>631389</t>
+          <t>633775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>678434</t>
+          <t>678758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1134626</t>
+          <t>1138489</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1193388</t>
+          <t>1192394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16711</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>22178</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>28906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>31134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21082</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28249</t>
+          <t>29977</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>24068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>37005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>49331</t>
+          <t>52808</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40584</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60028</t>
+          <t>63893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>110290</t>
+          <t>123061</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101453</t>
+          <t>114012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118458</t>
+          <t>130867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>129723</t>
+          <t>138875</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122113</t>
+          <t>130336</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137166</t>
+          <t>146158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240013</t>
+          <t>261935</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>226588</t>
+          <t>249816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249924</t>
+          <t>272515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>18106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27700</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41470</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23069</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24878</t>
+          <t>27417</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>43397</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47078</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>41135</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56104</t>
+          <t>62262</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>131757</t>
+          <t>148118</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123435</t>
+          <t>139684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138336</t>
+          <t>155654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166546</t>
+          <t>185139</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157147</t>
+          <t>174881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173942</t>
+          <t>194459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>298303</t>
+          <t>333256</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287103</t>
+          <t>320461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309721</t>
+          <t>345277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32063</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20498</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39240</t>
+          <t>31717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>121564</t>
+          <t>142892</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114360</t>
+          <t>135461</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126815</t>
+          <t>148891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>335846</t>
+          <t>147800</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>299903</t>
+          <t>139109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354324</t>
+          <t>155014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>457411</t>
+          <t>290692</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425224</t>
+          <t>278522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>485241</t>
+          <t>300614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>27469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25629</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>35963</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>27857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40487</t>
+          <t>45927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>54482</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40063</t>
+          <t>44600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>66661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172430</t>
+          <t>181690</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163624</t>
+          <t>172119</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179300</t>
+          <t>189127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>222627</t>
+          <t>236556</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212619</t>
+          <t>224849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232139</t>
+          <t>247063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>395057</t>
+          <t>418246</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381488</t>
+          <t>404024</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>406801</t>
+          <t>431230</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>203709</t>
+          <t>213625</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203709</t>
+          <t>213625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203709</t>
+          <t>213625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>479332</t>
+          <t>508991</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>479332</t>
+          <t>508991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479332</t>
+          <t>508991</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>48633</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>41588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59650</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>74999</t>
+          <t>80162</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39638</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99158</t>
+          <t>92568</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>123631</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80152</t>
+          <t>114706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147471</t>
+          <t>149219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63326</t>
+          <t>67234</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52417</t>
+          <t>54812</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76764</t>
+          <t>80640</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>104047</t>
+          <t>114813</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57215</t>
+          <t>102188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135659</t>
+          <t>132235</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>167373</t>
+          <t>182047</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108064</t>
+          <t>163107</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>198804</t>
+          <t>205064</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>536041</t>
+          <t>595762</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>519871</t>
+          <t>577990</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>549743</t>
+          <t>610069</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>854743</t>
+          <t>708369</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>801896</t>
+          <t>689630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>934419</t>
+          <t>724073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1390784</t>
+          <t>1304131</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1342454</t>
+          <t>1276180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1498299</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>648000</t>
+          <t>713999</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648000</t>
+          <t>713999</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648000</t>
+          <t>713999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1681789</t>
+          <t>1617342</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1681789</t>
+          <t>1617342</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1681789</t>
+          <t>1617342</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
